--- a/verification/report-samples/maintenance-full-field.xlsx
+++ b/verification/report-samples/maintenance-full-field.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="Full-field register" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Full-field register'!$A1:$L11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Full-field register'!$A1:$L13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Full-field register'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>Gujjar Brother Transport — TEST DATA ONLY</t>
   </si>
@@ -23,40 +23,40 @@
     <t>Selected period 2026-01-01 to 2026-12-31; current master records; loans cumulative through cutoff including opening principal.</t>
   </si>
   <si>
-    <t>vehical</t>
-  </si>
-  <si>
-    <t>driver</t>
-  </si>
-  <si>
-    <t>engine</t>
-  </si>
-  <si>
-    <t>gear</t>
-  </si>
-  <si>
-    <t>hissa</t>
-  </si>
-  <si>
-    <t>tyre</t>
-  </si>
-  <si>
-    <t>electrion wiring</t>
-  </si>
-  <si>
-    <t>elec self</t>
-  </si>
-  <si>
-    <t>elec genrater</t>
-  </si>
-  <si>
-    <t>elec lighting</t>
-  </si>
-  <si>
-    <t>cabin</t>
-  </si>
-  <si>
-    <t>body</t>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Engine</t>
+  </si>
+  <si>
+    <t>Gear</t>
+  </si>
+  <si>
+    <t>Hissa / parts</t>
+  </si>
+  <si>
+    <t>Tyre</t>
+  </si>
+  <si>
+    <t>Electrical wiring</t>
+  </si>
+  <si>
+    <t>Electric self / starter</t>
+  </si>
+  <si>
+    <t>Electric generator / alternator</t>
+  </si>
+  <si>
+    <t>Electric lighting</t>
+  </si>
+  <si>
+    <t>Cabin</t>
+  </si>
+  <si>
+    <t>Body</t>
   </si>
   <si>
     <t>TEST-001</t>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>TEST unposted body work detail</t>
+  </si>
+  <si>
+    <t>Signature: __________________________</t>
   </si>
 </sst>
 </file>
@@ -547,10 +550,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="12" width="22" style="1" customWidth="1"/>
+    <col min="1" max="6" width="22" style="1" customWidth="1"/>
+    <col min="7" max="10" width="30" style="1" customWidth="1"/>
+    <col min="11" max="12" width="22" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -769,6 +774,22 @@
         <v>25</v>
       </c>
     </row>
+    <row r="13" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+    </row>
   </sheetData>
   <autoFilter ref="A4:L4"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
